--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Specifies the accuracy or exactness of a dateTime value when only some portion of 
+    <t>Specifies the accuracy or exactness of a dateTime value when only some part of 
 the known/ usable precision of dateTime can be verified as accurate or exact and the rest is estimated or approximate.
 This extension is intended to explicitly communicate the accuracy
 of a dateTime value, such as full timestamp, year-only, year-month, date-only, or
@@ -340,10 +340,10 @@
 </t>
   </si>
   <si>
-    <t>Meaningful usable precision of the dateTime value</t>
-  </si>
-  <si>
-    <t>Indicates the precision that is verified as clinically exact or accurate.
+    <t>Precision level of the exact/ accurate part of dateTime value</t>
+  </si>
+  <si>
+    <t>Indicates the precision level that is verified as clinically exact or accurate.
 Examples include year-only, month-level, date-level,
 full timestamp precision or none.</t>
   </si>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datetime-accuracy-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
